--- a/assets/fixtures/persona-jane-doe/hunt/job-tracker.xlsx
+++ b/assets/fixtures/persona-jane-doe/hunt/job-tracker.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Read the JD and decide by 17 Oct</t>
+          <t>You: read the JD and decide by 17 Oct</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>14 Oct 2026: Link from a former colleague. IC role that owns the component library.</t>
+          <t>14 Oct 2026: Portfolio refresh in progress before applying || 14 Oct 2026: Link from a former colleague. IC role that owns the component library.</t>
         </is>
       </c>
     </row>
